--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1520,12 +1520,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>差別化ポイント</t>
+          <t>c04-josler-sougou-kousatsu-kakikata.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1028,10 +1028,14 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>b02-josler-160cases.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1768,10 +1768,14 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>c09-josler-byoreki-youyaku-29cases.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -976,12 +976,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>競合強い</t>
+          <t>b01-josler-shourei-touroku-kakikata.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1380,12 +1380,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>最重要記事</t>
+          <t>c01-josler-byoreki-youyaku-kakikata.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1484,10 +1484,14 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>c03-josler-byoreki-youyaku-reibun.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1640,10 +1640,14 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>c06-josler-nyuingo-keika-kakikata.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1692,10 +1692,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>c07-josler-bunken-inyo.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2760,10 +2760,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>e02-josler-manianai.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -776,12 +776,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>季節更新必要</t>
+          <t>a05-josler-kigen-shimekiri.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -680,10 +680,14 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>a03-josler-tsukaikata.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -3308,10 +3308,14 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>g02-naika-senmoni-itsu-kara.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2716,7 +2716,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>e01-josler-shinchoku-kanri.mdx</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -3360,10 +3360,14 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>g03-naika-senmoni-sankousho.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -4664,12 +4664,12 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>差別化・内科ナビ連携</t>
+          <t>j01-josler-ai-katsuyo.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -4824,10 +4824,14 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>j04-josler-jitan.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="25" customHeight="1">
       <c r="A89" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2048,10 +2048,14 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>d02-josler-byoreki-youyaku-junkanki.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2100,10 +2100,14 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>d03-josler-byoreki-youyaku-kokyuuki.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -632,10 +632,14 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>a02-josler-login.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2312,10 +2312,14 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>d07-josler-byoreki-youyaku-taisha.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1244,10 +1244,14 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>b06-josler-jiko-shousatsu-kakikata.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2760,12 +2760,12 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>e01-josler-shinchoku-kanri.mdx</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>ツール連携</t>
         </is>
       </c>
     </row>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>初期研修医の入口記事</t>
+          <t>n08-senkoui-program-erabikata.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1144,10 +1144,14 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>b04-josler-shikkanngun-ichiran.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2872,10 +2872,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>e03-josler-schedule.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>b07-josler-shourei-touroku-shounin-sarenai.mdx</t>
         </is>
       </c>
       <c r="J16" s="2" t="n"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>c10-josler-accept-reject.mdx</t>
         </is>
       </c>
       <c r="J27" s="2" t="n"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>c11-josler-ichijihyouka.mdx</t>
         </is>
       </c>
       <c r="J28" s="2" t="n"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>g06-naika-senmoni-goukakuritsu.mdx</t>
         </is>
       </c>
       <c r="J61" s="2" t="n"/>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>g07-naika-senmoni-nanido.mdx</t>
         </is>
       </c>
       <c r="J62" s="2" t="n"/>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -2528,10 +2528,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n"/>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>d11-josler-byoreki-youyaku-kyuukyuu.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -2576,10 +2580,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n"/>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>d12-josler-geka-shoukai-shourei.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2672,10 +2680,14 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n"/>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>d14-josler-gairai-shourei.mdx</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キーワード一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サマリー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="キーワード一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="サマリー" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$1:$J$139</definedName>
@@ -7904,7 +7904,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>c13-josler-byoreki-youyaku-mojisuu.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -8012,7 +8012,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>c15-josler-kensa-kekka-tani.mdx</t>
         </is>
       </c>
     </row>

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -3248,10 +3248,14 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="n"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>f04-josler-e-learning</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">

--- a/docs/keywords/naikanavi_keyword_list.xlsx
+++ b/docs/keywords/naikanavi_keyword_list.xlsx
@@ -7774,12 +7774,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>公開済</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>忘れがちな手続き</t>
+          <t>a15-josler-360do-hyouka</t>
         </is>
       </c>
     </row>
